--- a/data.xlsx
+++ b/data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\diss\articles\Executable_blueprint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F45252F-BAA9-41BB-97D9-0BC3E17A8A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31030290-A0E7-4092-AA0D-BEDF85098BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="pass" sheetId="2" r:id="rId1"/>
+    <sheet name="fail" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
   <si>
     <t>ID</t>
   </si>
@@ -347,6 +348,64 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CDE506-C67F-48A4-BE2A-72DAF3822C6B}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1121</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,36 +2,49 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\diss\articles\Executable_blueprint\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lair\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31030290-A0E7-4092-AA0D-BEDF85098BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3096C2-61FD-4EA8-9809-F9646EE6AE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="pass" sheetId="2" r:id="rId1"/>
-    <sheet name="fail" sheetId="1" r:id="rId2"/>
+    <sheet name="pass" sheetId="1" r:id="rId1"/>
+    <sheet name="fail" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
   <si>
     <t>ID</t>
   </si>
   <si>
     <t>area</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>S4</t>
+  </si>
+  <si>
+    <t>S5</t>
+  </si>
+  <si>
+    <t>S6</t>
   </si>
 </sst>
 </file>
@@ -41,10 +54,7 @@
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -68,7 +78,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -87,9 +97,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -103,7 +113,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -115,7 +125,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -127,12 +137,12 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -162,12 +172,29 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -197,9 +224,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -348,8 +392,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CDE506-C67F-48A4-BE2A-72DAF3822C6B}">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -361,43 +405,51 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>1123</v>
+        <v>5234.5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>1140</v>
+        <v>5312.8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="s">
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>1139</v>
+        <v>5287.1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="s">
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>1147</v>
+        <v>5198.6000000000004</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="s">
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>1121</v>
+        <v>5265.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>5221.8999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -406,8 +458,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -419,43 +471,51 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>1123</v>
+        <v>5042.3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>1200</v>
+        <v>5389.7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="s">
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>1199</v>
+        <v>5201.3999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="s">
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>1147</v>
+        <v>5487.2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="s">
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>1171</v>
+        <v>5312.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>4898.5</v>
       </c>
     </row>
   </sheetData>
